--- a/BONOS LOCALES.xlsx
+++ b/BONOS LOCALES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\comun\Documents\GitHub\Gest-Spa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D51E34-A363-4A83-AFC7-35A59E3A6ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4B974E-F0C7-4C3A-9887-DEA478B4E237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DDC18F45-467B-464C-8E34-5CF8EDEF5D93}"/>
   </bookViews>
